--- a/Dreamscape UCDD.xlsx
+++ b/Dreamscape UCDD.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcuon\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B0B7187-9DE1-4571-8CAD-E267B9C2DD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0BB210-207A-4811-A9C4-7FCE01F44633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" activeTab="1" xr2:uid="{48464307-1D47-4DCE-B539-55A02EB605FC}"/>
+    <workbookView xWindow="12192" yWindow="0" windowWidth="12480" windowHeight="14736" xr2:uid="{48464307-1D47-4DCE-B539-55A02EB605FC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Home Screen" sheetId="6" r:id="rId1"/>
-    <sheet name="Alarms" sheetId="1" r:id="rId2"/>
-    <sheet name="Meditation" sheetId="2" r:id="rId3"/>
-    <sheet name="Routine" sheetId="3" r:id="rId4"/>
-    <sheet name="Music" sheetId="4" r:id="rId5"/>
-    <sheet name="Watch_Link" sheetId="5" r:id="rId6"/>
+    <sheet name="Alarms" sheetId="1" r:id="rId1"/>
+    <sheet name="Meditation" sheetId="2" r:id="rId2"/>
+    <sheet name="Routine" sheetId="3" r:id="rId3"/>
+    <sheet name="Music" sheetId="4" r:id="rId4"/>
+    <sheet name="Watch_Link" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="103">
   <si>
     <t>Use Case Title</t>
   </si>
@@ -55,9 +54,6 @@
     <t>Create and set alarms</t>
   </si>
   <si>
-    <t>Primaray Actor</t>
-  </si>
-  <si>
     <t>User</t>
   </si>
   <si>
@@ -76,9 +72,6 @@
     <t>Precondition:</t>
   </si>
   <si>
-    <t>User must set a time for when they want the alarm to go off</t>
-  </si>
-  <si>
     <t>Postcondition</t>
   </si>
   <si>
@@ -88,9 +81,6 @@
     <t>Trigger:</t>
   </si>
   <si>
-    <t>Must be in the alarm tab to create alarms</t>
-  </si>
-  <si>
     <t>Main Success Scenario:</t>
   </si>
   <si>
@@ -124,30 +114,15 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>3.2 system pop-up on the button shows when the next alarm will go off</t>
-  </si>
-  <si>
     <t>Exception</t>
   </si>
   <si>
-    <t>The user cannot put in the same time as the current time or it will not ring</t>
-  </si>
-  <si>
-    <t>If the user wishes to not save changes, it will delete any changes they have made</t>
-  </si>
-  <si>
     <t>Create Meditation Tips</t>
   </si>
   <si>
     <t>Create meditation tips after snoozing alarm</t>
   </si>
   <si>
-    <t>Partial</t>
-  </si>
-  <si>
-    <t>Alarm must go off</t>
-  </si>
-  <si>
     <t>Meditation tip is created and displayed to the user</t>
   </si>
   <si>
@@ -157,9 +132,6 @@
     <t>Alarm sounds</t>
   </si>
   <si>
-    <t>1.1 displays an alart on the phone to snooze the alarm</t>
-  </si>
-  <si>
     <t>Snooze the alarm</t>
   </si>
   <si>
@@ -169,105 +141,42 @@
     <t>2.2 Welcoming message pops up</t>
   </si>
   <si>
-    <t>Meditation tip is auto-created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1 displays the meditation tip </t>
-  </si>
-  <si>
-    <t>Meditation tip saved into Tips tab</t>
-  </si>
-  <si>
-    <t>4.1 saves the message in its repective tab</t>
-  </si>
-  <si>
-    <t>If user misses alarm,</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>message doesn't pop up</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
     <t>App closes and resets</t>
   </si>
   <si>
     <t>If user closes out the app before tip display, the meditation tip is not created</t>
   </si>
   <si>
-    <t>If user is not a Premium member, the feature is voided and lock out for user</t>
-  </si>
-  <si>
     <t>Create Routine</t>
   </si>
   <si>
     <t>Create Routine using user sleep pattern</t>
   </si>
   <si>
-    <t>Premium</t>
-  </si>
-  <si>
     <t>Membership</t>
   </si>
   <si>
-    <t>user must have a premium membership</t>
-  </si>
-  <si>
     <t>Routine will be set and saved in their Routines tab</t>
   </si>
   <si>
-    <t>recognizing the sleeping pattern of the user</t>
-  </si>
-  <si>
     <t>User selects Routines tab</t>
   </si>
   <si>
-    <t>1.1 displays the routines window</t>
-  </si>
-  <si>
-    <t>1.2 gives option for the user to create a routine</t>
-  </si>
-  <si>
     <t>User selects Generate</t>
   </si>
   <si>
-    <t>2.1 initializes the AI</t>
-  </si>
-  <si>
     <t>AI reads user sleep data</t>
   </si>
   <si>
-    <t>3.1 reads data</t>
-  </si>
-  <si>
     <t>AI generates a routine</t>
   </si>
   <si>
-    <t>4.1 creates routine and displays it</t>
-  </si>
-  <si>
     <t>Routine is set, and saved</t>
   </si>
   <si>
-    <t>5.1 automatically set to user's schedule</t>
-  </si>
-  <si>
-    <t>5.2 saved in the routines tab</t>
-  </si>
-  <si>
     <t>If user is not premium, will not function</t>
   </si>
   <si>
-    <t>has no sleep data, can't make routine with no data</t>
-  </si>
-  <si>
-    <t>Play/link  Music</t>
-  </si>
-  <si>
     <t>Play music to sleep, relax, or meditate</t>
   </si>
   <si>
@@ -277,36 +186,18 @@
     <t>User must have premium membership</t>
   </si>
   <si>
-    <t>Music will play at the desired time length</t>
-  </si>
-  <si>
-    <t>selecting music in the music tab</t>
-  </si>
-  <si>
     <t>Select the music tab</t>
   </si>
   <si>
-    <t>1.1 displays the music playlists</t>
-  </si>
-  <si>
     <t>1.2 Shows the option to link with a playlist from a third-party app</t>
   </si>
   <si>
     <t xml:space="preserve">Select the music playist </t>
   </si>
   <si>
-    <t>2.1 displays the music in the playlist</t>
-  </si>
-  <si>
     <t>Set the time limit for the music</t>
   </si>
   <si>
-    <t>3.1 displays the time limit menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2 sets the time for music to stop playing </t>
-  </si>
-  <si>
     <t>Press play</t>
   </si>
   <si>
@@ -316,9 +207,6 @@
     <t>If the user has no membership, content is locked for them</t>
   </si>
   <si>
-    <t>Spodify link has errors and can't load the playlist</t>
-  </si>
-  <si>
     <t>Setting a time limit greater than the playlist total time play will stop playing automatically</t>
   </si>
   <si>
@@ -343,15 +231,6 @@
     <t>Press the + button</t>
   </si>
   <si>
-    <t>1.1 displays option to link a device</t>
-  </si>
-  <si>
-    <t>1.2 displays option to pair a device</t>
-  </si>
-  <si>
-    <t>Select the deviec you want to pair</t>
-  </si>
-  <si>
     <t>2.1 Device is Paired</t>
   </si>
   <si>
@@ -361,46 +240,115 @@
     <t>If the watch is not in pair mode, no device will be detected</t>
   </si>
   <si>
-    <t>Home Screen</t>
-  </si>
-  <si>
-    <t>Opening the app</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>App Must be installed</t>
-  </si>
-  <si>
-    <t>Home UI starts up and displays home menu</t>
-  </si>
-  <si>
-    <t>Clicking the App</t>
-  </si>
-  <si>
-    <t>1.1 Loading screen starts up</t>
-  </si>
-  <si>
-    <t>1.2 displays home menu to 5 tabs consider the features</t>
-  </si>
-  <si>
-    <t>Open app</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select a feature tab  </t>
-  </si>
-  <si>
-    <t>2.1 displays the UI specific to the feature</t>
-  </si>
-  <si>
-    <t>User has no premium membeship,</t>
-  </si>
-  <si>
-    <t>Ad pops up</t>
-  </si>
-  <si>
-    <t>alert saying they have no subscription to the app</t>
+    <t>3.2 System pop-up on the button shows when the next alarm will go off</t>
+  </si>
+  <si>
+    <t>1.1 Displays an alert on the phone to snooze the alarm</t>
+  </si>
+  <si>
+    <t>Message doesn't pop up</t>
+  </si>
+  <si>
+    <t>1.1 Displays the routines window</t>
+  </si>
+  <si>
+    <t>1.2 Gives option for the user to create a routine</t>
+  </si>
+  <si>
+    <t>2.1 Initializes the AI</t>
+  </si>
+  <si>
+    <t>3.1 Reads data</t>
+  </si>
+  <si>
+    <t>4.1 Creates routine and displays it</t>
+  </si>
+  <si>
+    <t>5.1 Automatically set to user's schedule</t>
+  </si>
+  <si>
+    <t>5.2 Saved in the routines tab</t>
+  </si>
+  <si>
+    <t>1.1 Displays option to link a device</t>
+  </si>
+  <si>
+    <t>1.2 Displays option to pair a device</t>
+  </si>
+  <si>
+    <t>1.1 Displays the music playlists</t>
+  </si>
+  <si>
+    <t>2.1 Displays the music in the playlist</t>
+  </si>
+  <si>
+    <t>3.1 Displays the time limit menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2 Sets the time for music to stop playing </t>
+  </si>
+  <si>
+    <t>Primary Actor</t>
+  </si>
+  <si>
+    <t>if user has no sleep data, can't make routine with no data</t>
+  </si>
+  <si>
+    <t>Ststem recognizes the sleeping pattern of the user</t>
+  </si>
+  <si>
+    <t>User must have a premium membership</t>
+  </si>
+  <si>
+    <t>Music will play for the desired time length</t>
+  </si>
+  <si>
+    <t>Play/Link  Music</t>
+  </si>
+  <si>
+    <t>Selecting music in the music tab</t>
+  </si>
+  <si>
+    <t>Spotify link has errors and can't load the playlist</t>
+  </si>
+  <si>
+    <t>Select the device you want to pair</t>
+  </si>
+  <si>
+    <t>When time strikes the alarm time</t>
+  </si>
+  <si>
+    <t>User must set the time for when the alarm goes off</t>
+  </si>
+  <si>
+    <t>1.1a</t>
+  </si>
+  <si>
+    <t>1.1b</t>
+  </si>
+  <si>
+    <t>If the user cannot put in the same time as the current time it, then the alarm will not ring</t>
+  </si>
+  <si>
+    <t>If the user wishes to not save changes by pressing 'Discard', it will delete any changes they have made</t>
+  </si>
+  <si>
+    <t>If user misses alarm after 3 mins,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3 Displays the meditation tip </t>
+  </si>
+  <si>
+    <t>2.4 Saves the message in its repective tab</t>
+  </si>
+  <si>
+    <t>Alarm must go off; User must be a premium member</t>
+  </si>
+  <si>
+    <t>2.5 Meditation tip is auto-created</t>
+  </si>
+  <si>
+    <t>2.6 Meditation tip saved into Tips tab</t>
   </si>
 </sst>
 </file>
@@ -784,212 +732,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7A496D-0305-4FED-A0CC-FD5DFAB7C814}">
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.5546875" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>2.1</v>
-      </c>
-      <c r="B21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C24" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A2E071A-4C62-4542-9764-AD355D3EAD51}">
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1019,67 +761,67 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1087,15 +829,15 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1103,10 +845,10 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1114,53 +856,53 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1"/>
     </row>
@@ -1169,7 +911,7 @@
         <v>2.1</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="C21" s="1"/>
     </row>
@@ -1178,7 +920,7 @@
         <v>3.1</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="C22" s="1"/>
     </row>
@@ -1187,7 +929,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1"/>
     </row>
@@ -1196,9 +938,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E028D3C-465E-48C8-95E4-3F86446E5F04}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" customWidth="1"/>
@@ -1211,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -1220,73 +962,73 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1294,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1305,75 +1047,73 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
+      <c r="A13" t="s">
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
+      <c r="A14" t="s">
+        <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1"/>
     </row>
@@ -1382,51 +1122,43 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C21" s="1"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C22" s="1"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B25" t="s">
-        <v>52</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5318D0E3-D39E-4B63-A61E-D3E0C9715B1B}">
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1440,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -1449,73 +1181,73 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1523,15 +1255,15 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1539,10 +1271,10 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1550,10 +1282,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1561,10 +1293,10 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1572,41 +1304,41 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1"/>
     </row>
@@ -1615,7 +1347,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1"/>
     </row>
@@ -1624,19 +1356,19 @@
         <v>3.1</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1"/>
     </row>
@@ -1645,7 +1377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{545DD42E-3A9A-4437-B9BB-E488131538F8}">
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1660,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -1669,73 +1401,73 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1743,15 +1475,15 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1759,10 +1491,10 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1770,18 +1502,18 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1789,39 +1521,39 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1"/>
     </row>
@@ -1830,7 +1562,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1"/>
     </row>
@@ -1839,7 +1571,7 @@
         <v>1.2</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" s="1"/>
     </row>
@@ -1848,13 +1580,13 @@
         <v>3.1</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1"/>
     </row>
@@ -1863,7 +1595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4ABE8C-4B64-4E92-996C-99A0F58C7710}">
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1878,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -1887,73 +1619,73 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1961,18 +1693,18 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1980,59 +1712,59 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1"/>
     </row>
@@ -2041,7 +1773,7 @@
         <v>2.1</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C21" s="1"/>
     </row>
